--- a/data/samples/samples/15-9-F-14_D06_2026-03-06.xlsx
+++ b/data/samples/samples/15-9-F-14_D06_2026-03-06.xlsx
@@ -1046,7 +1046,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>06:00 06:30 钻进至 2565.61 m，钻压 102 kN，转速 125 rpm，排量 32 L/s，钻时 10.9 m/h。</t>
+          <t>06:30 06:30 钻进至 2565.61 m，钻压 102 kN，转速 125 rpm，排量 32 L/s，钻时 10.9 m/h。</t>
         </is>
       </c>
     </row>
@@ -1060,14 +1060,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>11:00 11:15 循环调整泥浆性能，密度提至 1.09 g/cm3，漏斗粘度 39 s。</t>
+          <t>11:15 11:15 循环调整泥浆性能，密度提至 1.09 g/cm3，漏斗粘度 39 s。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>14:00 14:15 地质录井汇报：岩性为灰色细砂岩，荧光显示 1 级。</t>
+          <t>14:15 14:15 地质录井汇报：岩性为灰色细砂岩，荧光显示 1 级。</t>
         </is>
       </c>
     </row>
@@ -1081,14 +1081,14 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>20:00 20:15 起钻至 2570.55 m，期间无遇卡显示。</t>
+          <t>20:15 20:15 起钻至 2570.55 m，期间无遇卡显示。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>22:00 22:45 短起下检查井眼，返砂正常。</t>
+          <t>22:45 22:45 短起下检查井眼，返砂正常。</t>
         </is>
       </c>
     </row>
